--- a/Inventory/inventory.xlsx
+++ b/Inventory/inventory.xlsx
@@ -2230,7 +2230,7 @@
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I254"/>
+  <dimension ref="A1:J254"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2260,6 +2260,9 @@
       <c r="I1" t="str">
         <v>Label</v>
       </c>
+      <c r="J1" t="str">
+        <v>Hidden</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -2289,6 +2292,9 @@
       <c r="I2" t="str">
         <v/>
       </c>
+      <c r="J2" t="str">
+        <v/>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -2318,6 +2324,9 @@
       <c r="I3" t="str">
         <v/>
       </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -2347,6 +2356,9 @@
       <c r="I4" t="str">
         <v/>
       </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -2376,6 +2388,9 @@
       <c r="I5" t="str">
         <v/>
       </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -2405,6 +2420,9 @@
       <c r="I6" t="str">
         <v/>
       </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -2434,6 +2452,9 @@
       <c r="I7" t="str">
         <v/>
       </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -2463,6 +2484,9 @@
       <c r="I8" t="str">
         <v/>
       </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -2492,6 +2516,9 @@
       <c r="I9" t="str">
         <v/>
       </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -2521,6 +2548,9 @@
       <c r="I10" t="str">
         <v/>
       </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -2550,6 +2580,9 @@
       <c r="I11" t="str">
         <v/>
       </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -2579,6 +2612,9 @@
       <c r="I12" t="str">
         <v/>
       </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -2608,6 +2644,9 @@
       <c r="I13" t="str">
         <v/>
       </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
@@ -2637,6 +2676,9 @@
       <c r="I14" t="str">
         <v/>
       </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -2666,6 +2708,9 @@
       <c r="I15" t="str">
         <v/>
       </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -2695,6 +2740,9 @@
       <c r="I16" t="str">
         <v/>
       </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -2724,6 +2772,9 @@
       <c r="I17" t="str">
         <v/>
       </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -2753,6 +2804,9 @@
       <c r="I18" t="str">
         <v/>
       </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -2782,6 +2836,9 @@
       <c r="I19" t="str">
         <v/>
       </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -2811,6 +2868,9 @@
       <c r="I20" t="str">
         <v/>
       </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -2840,6 +2900,9 @@
       <c r="I21" t="str">
         <v/>
       </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
@@ -2869,6 +2932,9 @@
       <c r="I22" t="str">
         <v/>
       </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
@@ -2898,6 +2964,9 @@
       <c r="I23" t="str">
         <v/>
       </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
@@ -2927,6 +2996,9 @@
       <c r="I24" t="str">
         <v/>
       </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
@@ -2956,6 +3028,9 @@
       <c r="I25" t="str">
         <v/>
       </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
@@ -2985,6 +3060,9 @@
       <c r="I26" t="str">
         <v/>
       </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
@@ -3014,6 +3092,9 @@
       <c r="I27" t="str">
         <v/>
       </c>
+      <c r="J27" t="str">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
@@ -3043,6 +3124,9 @@
       <c r="I28" t="str">
         <v/>
       </c>
+      <c r="J28" t="str">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
@@ -3072,6 +3156,9 @@
       <c r="I29" t="str">
         <v/>
       </c>
+      <c r="J29" t="str">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
@@ -3101,6 +3188,9 @@
       <c r="I30" t="str">
         <v/>
       </c>
+      <c r="J30" t="str">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
@@ -3130,6 +3220,9 @@
       <c r="I31" t="str">
         <v/>
       </c>
+      <c r="J31" t="str">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
@@ -3159,6 +3252,9 @@
       <c r="I32" t="str">
         <v/>
       </c>
+      <c r="J32" t="str">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
@@ -3188,6 +3284,9 @@
       <c r="I33" t="str">
         <v/>
       </c>
+      <c r="J33" t="str">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
@@ -3217,6 +3316,9 @@
       <c r="I34" t="str">
         <v/>
       </c>
+      <c r="J34" t="str">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
@@ -3246,6 +3348,9 @@
       <c r="I35" t="str">
         <v/>
       </c>
+      <c r="J35" t="str">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
@@ -3275,6 +3380,9 @@
       <c r="I36" t="str">
         <v/>
       </c>
+      <c r="J36" t="str">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
@@ -3304,6 +3412,9 @@
       <c r="I37" t="str">
         <v/>
       </c>
+      <c r="J37" t="str">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
@@ -3333,6 +3444,9 @@
       <c r="I38" t="str">
         <v/>
       </c>
+      <c r="J38" t="str">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
@@ -3362,6 +3476,9 @@
       <c r="I39" t="str">
         <v/>
       </c>
+      <c r="J39" t="str">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
@@ -3391,6 +3508,9 @@
       <c r="I40" t="str">
         <v/>
       </c>
+      <c r="J40" t="str">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
@@ -3420,6 +3540,9 @@
       <c r="I41" t="str">
         <v/>
       </c>
+      <c r="J41" t="str">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
@@ -3449,6 +3572,9 @@
       <c r="I42" t="str">
         <v/>
       </c>
+      <c r="J42" t="str">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
@@ -3478,6 +3604,9 @@
       <c r="I43" t="str">
         <v/>
       </c>
+      <c r="J43" t="str">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
@@ -3507,6 +3636,9 @@
       <c r="I44" t="str">
         <v/>
       </c>
+      <c r="J44" t="str">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
@@ -3536,6 +3668,9 @@
       <c r="I45" t="str">
         <v/>
       </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
@@ -3565,6 +3700,9 @@
       <c r="I46" t="str">
         <v/>
       </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
@@ -3594,6 +3732,9 @@
       <c r="I47" t="str">
         <v/>
       </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -3623,6 +3764,9 @@
       <c r="I48" t="str">
         <v/>
       </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
@@ -3652,6 +3796,9 @@
       <c r="I49" t="str">
         <v/>
       </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
@@ -3681,6 +3828,9 @@
       <c r="I50" t="str">
         <v/>
       </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
@@ -3710,6 +3860,9 @@
       <c r="I51" t="str">
         <v/>
       </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
@@ -3739,6 +3892,9 @@
       <c r="I52" t="str">
         <v/>
       </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
@@ -3768,6 +3924,9 @@
       <c r="I53" t="str">
         <v/>
       </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
@@ -3797,6 +3956,9 @@
       <c r="I54" t="str">
         <v/>
       </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
@@ -3826,6 +3988,9 @@
       <c r="I55" t="str">
         <v/>
       </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
@@ -3855,6 +4020,9 @@
       <c r="I56" t="str">
         <v/>
       </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
@@ -3884,6 +4052,9 @@
       <c r="I57" t="str">
         <v/>
       </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
@@ -3913,6 +4084,9 @@
       <c r="I58" t="str">
         <v/>
       </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
@@ -3942,6 +4116,9 @@
       <c r="I59" t="str">
         <v/>
       </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
@@ -3971,6 +4148,9 @@
       <c r="I60" t="str">
         <v/>
       </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
@@ -4000,6 +4180,9 @@
       <c r="I61" t="str">
         <v/>
       </c>
+      <c r="J61" t="str">
+        <v/>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
@@ -4029,6 +4212,9 @@
       <c r="I62" t="str">
         <v/>
       </c>
+      <c r="J62" t="str">
+        <v/>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
@@ -4058,6 +4244,9 @@
       <c r="I63" t="str">
         <v/>
       </c>
+      <c r="J63" t="str">
+        <v/>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
@@ -4087,6 +4276,9 @@
       <c r="I64" t="str">
         <v/>
       </c>
+      <c r="J64" t="str">
+        <v/>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
@@ -4116,6 +4308,9 @@
       <c r="I65" t="str">
         <v/>
       </c>
+      <c r="J65" t="str">
+        <v/>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
@@ -4145,6 +4340,9 @@
       <c r="I66" t="str">
         <v/>
       </c>
+      <c r="J66" t="str">
+        <v/>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
@@ -4174,6 +4372,9 @@
       <c r="I67" t="str">
         <v/>
       </c>
+      <c r="J67" t="str">
+        <v/>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
@@ -4203,6 +4404,9 @@
       <c r="I68" t="str">
         <v/>
       </c>
+      <c r="J68" t="str">
+        <v/>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
@@ -4232,6 +4436,9 @@
       <c r="I69" t="str">
         <v/>
       </c>
+      <c r="J69" t="str">
+        <v/>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
@@ -4261,6 +4468,9 @@
       <c r="I70" t="str">
         <v/>
       </c>
+      <c r="J70" t="str">
+        <v/>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
@@ -4290,6 +4500,9 @@
       <c r="I71" t="str">
         <v/>
       </c>
+      <c r="J71" t="str">
+        <v/>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
@@ -4319,6 +4532,9 @@
       <c r="I72" t="str">
         <v/>
       </c>
+      <c r="J72" t="str">
+        <v/>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
@@ -4348,6 +4564,9 @@
       <c r="I73" t="str">
         <v/>
       </c>
+      <c r="J73" t="str">
+        <v/>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
@@ -4377,6 +4596,9 @@
       <c r="I74" t="str">
         <v/>
       </c>
+      <c r="J74" t="str">
+        <v/>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
@@ -4406,6 +4628,9 @@
       <c r="I75" t="str">
         <v/>
       </c>
+      <c r="J75" t="str">
+        <v/>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
@@ -4435,6 +4660,9 @@
       <c r="I76" t="str">
         <v/>
       </c>
+      <c r="J76" t="str">
+        <v/>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
@@ -4464,6 +4692,9 @@
       <c r="I77" t="str">
         <v/>
       </c>
+      <c r="J77" t="str">
+        <v/>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
@@ -4493,6 +4724,9 @@
       <c r="I78" t="str">
         <v/>
       </c>
+      <c r="J78" t="str">
+        <v/>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
@@ -4522,6 +4756,9 @@
       <c r="I79" t="str">
         <v/>
       </c>
+      <c r="J79" t="str">
+        <v/>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
@@ -4551,6 +4788,9 @@
       <c r="I80" t="str">
         <v/>
       </c>
+      <c r="J80" t="str">
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
@@ -4580,6 +4820,9 @@
       <c r="I81" t="str">
         <v/>
       </c>
+      <c r="J81" t="str">
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
@@ -4609,6 +4852,9 @@
       <c r="I82" t="str">
         <v/>
       </c>
+      <c r="J82" t="str">
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
@@ -4638,6 +4884,9 @@
       <c r="I83" t="str">
         <v/>
       </c>
+      <c r="J83" t="str">
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
@@ -4667,6 +4916,9 @@
       <c r="I84" t="str">
         <v/>
       </c>
+      <c r="J84" t="str">
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
@@ -4696,6 +4948,9 @@
       <c r="I85" t="str">
         <v/>
       </c>
+      <c r="J85" t="str">
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
@@ -4751,6 +5006,9 @@
       <c r="I87" t="str">
         <v/>
       </c>
+      <c r="J87" t="str">
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
@@ -4780,6 +5038,9 @@
       <c r="I88" t="str">
         <v/>
       </c>
+      <c r="J88" t="str">
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
@@ -4809,6 +5070,9 @@
       <c r="I89" t="str">
         <v/>
       </c>
+      <c r="J89" t="str">
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
@@ -4838,6 +5102,9 @@
       <c r="I90" t="str">
         <v/>
       </c>
+      <c r="J90" t="str">
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
@@ -4867,6 +5134,9 @@
       <c r="I91" t="str">
         <v/>
       </c>
+      <c r="J91" t="str">
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
@@ -4896,6 +5166,9 @@
       <c r="I92" t="str">
         <v/>
       </c>
+      <c r="J92" t="str">
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
@@ -4925,6 +5198,9 @@
       <c r="I93" t="str">
         <v/>
       </c>
+      <c r="J93" t="str">
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
@@ -4954,6 +5230,9 @@
       <c r="I94" t="str">
         <v/>
       </c>
+      <c r="J94" t="str">
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
@@ -4983,6 +5262,9 @@
       <c r="I95" t="str">
         <v/>
       </c>
+      <c r="J95" t="str">
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
@@ -5012,6 +5294,9 @@
       <c r="I96" t="str">
         <v/>
       </c>
+      <c r="J96" t="str">
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
@@ -5041,6 +5326,9 @@
       <c r="I97" t="str">
         <v/>
       </c>
+      <c r="J97" t="str">
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
@@ -5070,6 +5358,9 @@
       <c r="I98" t="str">
         <v/>
       </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
@@ -5099,6 +5390,9 @@
       <c r="I99" t="str">
         <v/>
       </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
@@ -5128,6 +5422,9 @@
       <c r="I100" t="str">
         <v/>
       </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
@@ -5157,6 +5454,9 @@
       <c r="I101" t="str">
         <v/>
       </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
@@ -5186,6 +5486,9 @@
       <c r="I102" t="str">
         <v/>
       </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
@@ -5215,6 +5518,9 @@
       <c r="I103" t="str">
         <v/>
       </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
@@ -5244,6 +5550,9 @@
       <c r="I104" t="str">
         <v/>
       </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
@@ -5273,6 +5582,9 @@
       <c r="I105" t="str">
         <v/>
       </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
@@ -5302,6 +5614,9 @@
       <c r="I106" t="str">
         <v/>
       </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
@@ -5331,6 +5646,9 @@
       <c r="I107" t="str">
         <v/>
       </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
@@ -5360,6 +5678,9 @@
       <c r="I108" t="str">
         <v/>
       </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
@@ -5389,6 +5710,9 @@
       <c r="I109" t="str">
         <v/>
       </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
@@ -5418,6 +5742,9 @@
       <c r="I110" t="str">
         <v/>
       </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
@@ -5447,6 +5774,9 @@
       <c r="I111" t="str">
         <v/>
       </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
@@ -5476,6 +5806,9 @@
       <c r="I112" t="str">
         <v/>
       </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
@@ -5505,6 +5838,9 @@
       <c r="I113" t="str">
         <v/>
       </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
@@ -5534,6 +5870,9 @@
       <c r="I114" t="str">
         <v/>
       </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
@@ -5563,6 +5902,9 @@
       <c r="I115" t="str">
         <v/>
       </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
@@ -5592,6 +5934,9 @@
       <c r="I116" t="str">
         <v/>
       </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
@@ -5621,6 +5966,9 @@
       <c r="I117" t="str">
         <v/>
       </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
@@ -5650,6 +5998,9 @@
       <c r="I118" t="str">
         <v/>
       </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
@@ -5679,6 +6030,9 @@
       <c r="I119" t="str">
         <v/>
       </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
@@ -5708,6 +6062,9 @@
       <c r="I120" t="str">
         <v/>
       </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
@@ -5737,6 +6094,9 @@
       <c r="I121" t="str">
         <v/>
       </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
@@ -5766,6 +6126,9 @@
       <c r="I122" t="str">
         <v/>
       </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
@@ -5795,6 +6158,9 @@
       <c r="I123" t="str">
         <v/>
       </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
@@ -5824,6 +6190,9 @@
       <c r="I124" t="str">
         <v/>
       </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
@@ -5853,6 +6222,9 @@
       <c r="I125" t="str">
         <v/>
       </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
@@ -5882,6 +6254,9 @@
       <c r="I126" t="str">
         <v/>
       </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
@@ -5911,6 +6286,9 @@
       <c r="I127" t="str">
         <v/>
       </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
@@ -5940,6 +6318,9 @@
       <c r="I128" t="str">
         <v/>
       </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
@@ -5995,6 +6376,9 @@
       <c r="I130" t="str">
         <v/>
       </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
@@ -6024,6 +6408,9 @@
       <c r="I131" t="str">
         <v/>
       </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
@@ -6053,6 +6440,9 @@
       <c r="I132" t="str">
         <v/>
       </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
@@ -6082,6 +6472,9 @@
       <c r="I133" t="str">
         <v/>
       </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
@@ -6111,6 +6504,9 @@
       <c r="I134" t="str">
         <v/>
       </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
@@ -6140,6 +6536,9 @@
       <c r="I135" t="str">
         <v/>
       </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
@@ -6169,6 +6568,9 @@
       <c r="I136" t="str">
         <v/>
       </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
@@ -6198,6 +6600,9 @@
       <c r="I137" t="str">
         <v/>
       </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
@@ -6227,6 +6632,9 @@
       <c r="I138" t="str">
         <v/>
       </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
@@ -6256,6 +6664,9 @@
       <c r="I139" t="str">
         <v/>
       </c>
+      <c r="J139" t="str">
+        <v/>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
@@ -6285,6 +6696,9 @@
       <c r="I140" t="str">
         <v/>
       </c>
+      <c r="J140" t="str">
+        <v/>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
@@ -6314,6 +6728,9 @@
       <c r="I141" t="str">
         <v/>
       </c>
+      <c r="J141" t="str">
+        <v/>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
@@ -6343,6 +6760,9 @@
       <c r="I142" t="str">
         <v/>
       </c>
+      <c r="J142" t="str">
+        <v/>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
@@ -6372,6 +6792,9 @@
       <c r="I143" t="str">
         <v/>
       </c>
+      <c r="J143" t="str">
+        <v/>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
@@ -6401,6 +6824,9 @@
       <c r="I144" t="str">
         <v/>
       </c>
+      <c r="J144" t="str">
+        <v/>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
@@ -6430,6 +6856,9 @@
       <c r="I145" t="str">
         <v/>
       </c>
+      <c r="J145" t="str">
+        <v/>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
@@ -6459,6 +6888,9 @@
       <c r="I146" t="str">
         <v/>
       </c>
+      <c r="J146" t="str">
+        <v/>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
@@ -6488,6 +6920,9 @@
       <c r="I147" t="str">
         <v/>
       </c>
+      <c r="J147" t="str">
+        <v/>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
@@ -6517,6 +6952,9 @@
       <c r="I148" t="str">
         <v/>
       </c>
+      <c r="J148" t="str">
+        <v/>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
@@ -6546,6 +6984,9 @@
       <c r="I149" t="str">
         <v/>
       </c>
+      <c r="J149" t="str">
+        <v/>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
@@ -6575,6 +7016,9 @@
       <c r="I150" t="str">
         <v/>
       </c>
+      <c r="J150" t="str">
+        <v/>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
@@ -6604,6 +7048,9 @@
       <c r="I151" t="str">
         <v/>
       </c>
+      <c r="J151" t="str">
+        <v/>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
@@ -6633,6 +7080,9 @@
       <c r="I152" t="str">
         <v/>
       </c>
+      <c r="J152" t="str">
+        <v/>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
@@ -6662,6 +7112,9 @@
       <c r="I153" t="str">
         <v/>
       </c>
+      <c r="J153" t="str">
+        <v/>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
@@ -6691,6 +7144,9 @@
       <c r="I154" t="str">
         <v/>
       </c>
+      <c r="J154" t="str">
+        <v/>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
@@ -6720,6 +7176,9 @@
       <c r="I155" t="str">
         <v/>
       </c>
+      <c r="J155" t="str">
+        <v/>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
@@ -6749,6 +7208,9 @@
       <c r="I156" t="str">
         <v/>
       </c>
+      <c r="J156" t="str">
+        <v/>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
@@ -6778,6 +7240,9 @@
       <c r="I157" t="str">
         <v/>
       </c>
+      <c r="J157" t="str">
+        <v/>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
@@ -6807,6 +7272,9 @@
       <c r="I158" t="str">
         <v/>
       </c>
+      <c r="J158" t="str">
+        <v/>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
@@ -6836,6 +7304,9 @@
       <c r="I159" t="str">
         <v/>
       </c>
+      <c r="J159" t="str">
+        <v/>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
@@ -6865,6 +7336,9 @@
       <c r="I160" t="str">
         <v/>
       </c>
+      <c r="J160" t="str">
+        <v/>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
@@ -6894,6 +7368,9 @@
       <c r="I161" t="str">
         <v/>
       </c>
+      <c r="J161" t="str">
+        <v/>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
@@ -6923,6 +7400,9 @@
       <c r="I162" t="str">
         <v/>
       </c>
+      <c r="J162" t="str">
+        <v/>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
@@ -6952,6 +7432,9 @@
       <c r="I163" t="str">
         <v/>
       </c>
+      <c r="J163" t="str">
+        <v/>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
@@ -6981,6 +7464,9 @@
       <c r="I164" t="str">
         <v/>
       </c>
+      <c r="J164" t="str">
+        <v/>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
@@ -7010,6 +7496,9 @@
       <c r="I165" t="str">
         <v/>
       </c>
+      <c r="J165" t="str">
+        <v/>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
@@ -7039,6 +7528,9 @@
       <c r="I166" t="str">
         <v/>
       </c>
+      <c r="J166" t="str">
+        <v/>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
@@ -7068,6 +7560,9 @@
       <c r="I167" t="str">
         <v/>
       </c>
+      <c r="J167" t="str">
+        <v/>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
@@ -7097,6 +7592,9 @@
       <c r="I168" t="str">
         <v/>
       </c>
+      <c r="J168" t="str">
+        <v/>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
@@ -7126,6 +7624,9 @@
       <c r="I169" t="str">
         <v/>
       </c>
+      <c r="J169" t="str">
+        <v/>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
@@ -7155,6 +7656,9 @@
       <c r="I170" t="str">
         <v/>
       </c>
+      <c r="J170" t="str">
+        <v/>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
@@ -7184,6 +7688,9 @@
       <c r="I171" t="str">
         <v/>
       </c>
+      <c r="J171" t="str">
+        <v/>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
@@ -7213,6 +7720,9 @@
       <c r="I172" t="str">
         <v/>
       </c>
+      <c r="J172" t="str">
+        <v/>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
@@ -7242,6 +7752,9 @@
       <c r="I173" t="str">
         <v/>
       </c>
+      <c r="J173" t="str">
+        <v/>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
@@ -7271,6 +7784,9 @@
       <c r="I174" t="str">
         <v/>
       </c>
+      <c r="J174" t="str">
+        <v/>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
@@ -7300,6 +7816,9 @@
       <c r="I175" t="str">
         <v/>
       </c>
+      <c r="J175" t="str">
+        <v/>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
@@ -7329,6 +7848,9 @@
       <c r="I176" t="str">
         <v/>
       </c>
+      <c r="J176" t="str">
+        <v/>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
@@ -7358,6 +7880,9 @@
       <c r="I177" t="str">
         <v/>
       </c>
+      <c r="J177" t="str">
+        <v/>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
@@ -7387,6 +7912,9 @@
       <c r="I178" t="str">
         <v/>
       </c>
+      <c r="J178" t="str">
+        <v/>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
@@ -7416,6 +7944,9 @@
       <c r="I179" t="str">
         <v/>
       </c>
+      <c r="J179" t="str">
+        <v/>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
@@ -7445,6 +7976,9 @@
       <c r="I180" t="str">
         <v/>
       </c>
+      <c r="J180" t="str">
+        <v/>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
@@ -7474,6 +8008,9 @@
       <c r="I181" t="str">
         <v/>
       </c>
+      <c r="J181" t="str">
+        <v/>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
@@ -7503,6 +8040,9 @@
       <c r="I182" t="str">
         <v/>
       </c>
+      <c r="J182" t="str">
+        <v/>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
@@ -7532,6 +8072,9 @@
       <c r="I183" t="str">
         <v/>
       </c>
+      <c r="J183" t="str">
+        <v/>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
@@ -7561,6 +8104,9 @@
       <c r="I184" t="str">
         <v/>
       </c>
+      <c r="J184" t="str">
+        <v/>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
@@ -7590,6 +8136,9 @@
       <c r="I185" t="str">
         <v/>
       </c>
+      <c r="J185" t="str">
+        <v/>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
@@ -7619,6 +8168,9 @@
       <c r="I186" t="str">
         <v/>
       </c>
+      <c r="J186" t="str">
+        <v/>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
@@ -7648,6 +8200,9 @@
       <c r="I187" t="str">
         <v/>
       </c>
+      <c r="J187" t="str">
+        <v/>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
@@ -7677,6 +8232,9 @@
       <c r="I188" t="str">
         <v/>
       </c>
+      <c r="J188" t="str">
+        <v/>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
@@ -7706,6 +8264,9 @@
       <c r="I189" t="str">
         <v/>
       </c>
+      <c r="J189" t="str">
+        <v/>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
@@ -7735,6 +8296,9 @@
       <c r="I190" t="str">
         <v/>
       </c>
+      <c r="J190" t="str">
+        <v/>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
@@ -7764,6 +8328,9 @@
       <c r="I191" t="str">
         <v/>
       </c>
+      <c r="J191" t="str">
+        <v/>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
@@ -7793,6 +8360,9 @@
       <c r="I192" t="str">
         <v/>
       </c>
+      <c r="J192" t="str">
+        <v/>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
@@ -7822,6 +8392,9 @@
       <c r="I193" t="str">
         <v/>
       </c>
+      <c r="J193" t="str">
+        <v/>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
@@ -7851,6 +8424,9 @@
       <c r="I194" t="str">
         <v/>
       </c>
+      <c r="J194" t="str">
+        <v/>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
@@ -7880,6 +8456,9 @@
       <c r="I195" t="str">
         <v/>
       </c>
+      <c r="J195" t="str">
+        <v/>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
@@ -7909,6 +8488,9 @@
       <c r="I196" t="str">
         <v/>
       </c>
+      <c r="J196" t="str">
+        <v/>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
@@ -7938,6 +8520,9 @@
       <c r="I197" t="str">
         <v/>
       </c>
+      <c r="J197" t="str">
+        <v/>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
@@ -7967,6 +8552,9 @@
       <c r="I198" t="str">
         <v/>
       </c>
+      <c r="J198" t="str">
+        <v/>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
@@ -7996,6 +8584,9 @@
       <c r="I199" t="str">
         <v/>
       </c>
+      <c r="J199" t="str">
+        <v/>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
@@ -8025,6 +8616,9 @@
       <c r="I200" t="str">
         <v/>
       </c>
+      <c r="J200" t="str">
+        <v/>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
@@ -8054,6 +8648,9 @@
       <c r="I201" t="str">
         <v/>
       </c>
+      <c r="J201" t="str">
+        <v/>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
@@ -8083,6 +8680,9 @@
       <c r="I202" t="str">
         <v/>
       </c>
+      <c r="J202" t="str">
+        <v/>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
@@ -8112,6 +8712,9 @@
       <c r="I203" t="str">
         <v/>
       </c>
+      <c r="J203" t="str">
+        <v/>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
@@ -8141,6 +8744,9 @@
       <c r="I204" t="str">
         <v/>
       </c>
+      <c r="J204" t="str">
+        <v/>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
@@ -8170,6 +8776,9 @@
       <c r="I205" t="str">
         <v/>
       </c>
+      <c r="J205" t="str">
+        <v/>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
@@ -8199,6 +8808,9 @@
       <c r="I206" t="str">
         <v/>
       </c>
+      <c r="J206" t="str">
+        <v/>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
@@ -8228,6 +8840,9 @@
       <c r="I207" t="str">
         <v/>
       </c>
+      <c r="J207" t="str">
+        <v/>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="str">
@@ -8257,6 +8872,9 @@
       <c r="I208" t="str">
         <v/>
       </c>
+      <c r="J208" t="str">
+        <v/>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="str">
@@ -8286,6 +8904,9 @@
       <c r="I209" t="str">
         <v/>
       </c>
+      <c r="J209" t="str">
+        <v/>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="str">
@@ -8315,6 +8936,9 @@
       <c r="I210" t="str">
         <v/>
       </c>
+      <c r="J210" t="str">
+        <v/>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="str">
@@ -8344,6 +8968,9 @@
       <c r="I211" t="str">
         <v/>
       </c>
+      <c r="J211" t="str">
+        <v/>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="str">
@@ -8373,6 +9000,9 @@
       <c r="I212" t="str">
         <v/>
       </c>
+      <c r="J212" t="str">
+        <v/>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="str">
@@ -8402,6 +9032,9 @@
       <c r="I213" t="str">
         <v/>
       </c>
+      <c r="J213" t="str">
+        <v/>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="str">
@@ -8431,6 +9064,9 @@
       <c r="I214" t="str">
         <v/>
       </c>
+      <c r="J214" t="str">
+        <v/>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="str">
@@ -8460,6 +9096,9 @@
       <c r="I215" t="str">
         <v/>
       </c>
+      <c r="J215" t="str">
+        <v/>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="str">
@@ -8515,6 +9154,9 @@
       <c r="I217" t="str">
         <v/>
       </c>
+      <c r="J217" t="str">
+        <v/>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="str">
@@ -8544,6 +9186,9 @@
       <c r="I218" t="str">
         <v/>
       </c>
+      <c r="J218" t="str">
+        <v/>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="str">
@@ -8573,6 +9218,9 @@
       <c r="I219" t="str">
         <v/>
       </c>
+      <c r="J219" t="str">
+        <v/>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="str">
@@ -8602,6 +9250,9 @@
       <c r="I220" t="str">
         <v/>
       </c>
+      <c r="J220" t="str">
+        <v/>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="str">
@@ -8631,6 +9282,9 @@
       <c r="I221" t="str">
         <v/>
       </c>
+      <c r="J221" t="str">
+        <v/>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="str">
@@ -8660,6 +9314,9 @@
       <c r="I222" t="str">
         <v/>
       </c>
+      <c r="J222" t="str">
+        <v/>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="str">
@@ -8689,6 +9346,9 @@
       <c r="I223" t="str">
         <v/>
       </c>
+      <c r="J223" t="str">
+        <v/>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="str">
@@ -8718,6 +9378,9 @@
       <c r="I224" t="str">
         <v/>
       </c>
+      <c r="J224" t="str">
+        <v/>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="str">
@@ -8747,6 +9410,9 @@
       <c r="I225" t="str">
         <v/>
       </c>
+      <c r="J225" t="str">
+        <v/>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="str">
@@ -8776,6 +9442,9 @@
       <c r="I226" t="str">
         <v/>
       </c>
+      <c r="J226" t="str">
+        <v/>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="str">
@@ -8805,6 +9474,9 @@
       <c r="I227" t="str">
         <v/>
       </c>
+      <c r="J227" t="str">
+        <v/>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="str">
@@ -8834,6 +9506,9 @@
       <c r="I228" t="str">
         <v/>
       </c>
+      <c r="J228" t="str">
+        <v/>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="str">
@@ -8863,6 +9538,9 @@
       <c r="I229" t="str">
         <v/>
       </c>
+      <c r="J229" t="str">
+        <v/>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="str">
@@ -8892,6 +9570,9 @@
       <c r="I230" t="str">
         <v/>
       </c>
+      <c r="J230" t="str">
+        <v/>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="str">
@@ -8921,6 +9602,9 @@
       <c r="I231" t="str">
         <v/>
       </c>
+      <c r="J231" t="str">
+        <v/>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="str">
@@ -8950,6 +9634,9 @@
       <c r="I232" t="str">
         <v/>
       </c>
+      <c r="J232" t="str">
+        <v/>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="str">
@@ -8979,6 +9666,9 @@
       <c r="I233" t="str">
         <v/>
       </c>
+      <c r="J233" t="str">
+        <v/>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="str">
@@ -9008,6 +9698,9 @@
       <c r="I234" t="str">
         <v/>
       </c>
+      <c r="J234" t="str">
+        <v/>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="str">
@@ -9037,6 +9730,9 @@
       <c r="I235" t="str">
         <v/>
       </c>
+      <c r="J235" t="str">
+        <v/>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="str">
@@ -9066,6 +9762,9 @@
       <c r="I236" t="str">
         <v/>
       </c>
+      <c r="J236" t="str">
+        <v/>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="str">
@@ -9095,6 +9794,9 @@
       <c r="I237" t="str">
         <v/>
       </c>
+      <c r="J237" t="str">
+        <v/>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="str">
@@ -9124,6 +9826,9 @@
       <c r="I238" t="str">
         <v/>
       </c>
+      <c r="J238" t="str">
+        <v/>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="str">
@@ -9153,6 +9858,9 @@
       <c r="I239" t="str">
         <v/>
       </c>
+      <c r="J239" t="str">
+        <v/>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="str">
@@ -9182,6 +9890,9 @@
       <c r="I240" t="str">
         <v/>
       </c>
+      <c r="J240" t="str">
+        <v/>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="str">
@@ -9211,6 +9922,9 @@
       <c r="I241" t="str">
         <v/>
       </c>
+      <c r="J241" t="str">
+        <v/>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="str">
@@ -9240,6 +9954,9 @@
       <c r="I242" t="str">
         <v/>
       </c>
+      <c r="J242" t="str">
+        <v/>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="str">
@@ -9269,6 +9986,9 @@
       <c r="I243" t="str">
         <v/>
       </c>
+      <c r="J243" t="str">
+        <v/>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="str">
@@ -9298,6 +10018,9 @@
       <c r="I244" t="str">
         <v/>
       </c>
+      <c r="J244" t="str">
+        <v/>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="str">
@@ -9327,6 +10050,9 @@
       <c r="I245" t="str">
         <v/>
       </c>
+      <c r="J245" t="str">
+        <v/>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="str">
@@ -9356,6 +10082,9 @@
       <c r="I246" t="str">
         <v/>
       </c>
+      <c r="J246" t="str">
+        <v/>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="str">
@@ -9385,6 +10114,9 @@
       <c r="I247" t="str">
         <v/>
       </c>
+      <c r="J247" t="str">
+        <v/>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="str">
@@ -9414,6 +10146,9 @@
       <c r="I248" t="str">
         <v/>
       </c>
+      <c r="J248" t="str">
+        <v/>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="str">
@@ -9443,6 +10178,9 @@
       <c r="I249" t="str">
         <v/>
       </c>
+      <c r="J249" t="str">
+        <v/>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="str">
@@ -9472,6 +10210,9 @@
       <c r="I250" t="str">
         <v/>
       </c>
+      <c r="J250" t="str">
+        <v/>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="str">
@@ -9501,6 +10242,9 @@
       <c r="I251" t="str">
         <v/>
       </c>
+      <c r="J251" t="str">
+        <v/>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="str">
@@ -9530,6 +10274,9 @@
       <c r="I252" t="str">
         <v/>
       </c>
+      <c r="J252" t="str">
+        <v/>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="str">
@@ -9559,6 +10306,9 @@
       <c r="I253" t="str">
         <v/>
       </c>
+      <c r="J253" t="str">
+        <v/>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="str">
@@ -9588,10 +10338,13 @@
       <c r="I254" t="str">
         <v/>
       </c>
+      <c r="J254" t="str">
+        <v/>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I254"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J254"/>
   </ignoredErrors>
 </worksheet>
 </file>
